--- a/Алгоритм диагностики.xlsx
+++ b/Алгоритм диагностики.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="874" activeTab="16"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="874" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Z5R" sheetId="3" r:id="rId1"/>
@@ -14,16 +14,17 @@
     <sheet name="Z5R Web BT" sheetId="8" r:id="rId5"/>
     <sheet name="Matrix-II EK(K)" sheetId="9" r:id="rId6"/>
     <sheet name="Matrix-II EK Net" sheetId="17" r:id="rId7"/>
-    <sheet name="Matrix-II MF-I" sheetId="13" r:id="rId8"/>
-    <sheet name="Matrix-II EH" sheetId="14" r:id="rId9"/>
-    <sheet name="Matrix-III EH" sheetId="2" r:id="rId10"/>
-    <sheet name="Matrix-III RD ALL" sheetId="6" r:id="rId11"/>
-    <sheet name="IL-102" sheetId="5" r:id="rId12"/>
-    <sheet name="CP-Z-2 EP" sheetId="15" r:id="rId13"/>
-    <sheet name="CP-Z-2 MF-I" sheetId="16" r:id="rId14"/>
-    <sheet name="CP-Z-2-B" sheetId="7" r:id="rId15"/>
-    <sheet name="Z-397 Guard" sheetId="10" r:id="rId16"/>
-    <sheet name="Z-397 Web" sheetId="11" r:id="rId17"/>
+    <sheet name="Matrix-II EK WIFI" sheetId="18" r:id="rId8"/>
+    <sheet name="Matrix-II MF-I" sheetId="13" r:id="rId9"/>
+    <sheet name="Matrix-II EH" sheetId="14" r:id="rId10"/>
+    <sheet name="Matrix-III EH" sheetId="2" r:id="rId11"/>
+    <sheet name="Matrix-III RD ALL" sheetId="6" r:id="rId12"/>
+    <sheet name="IL-102" sheetId="5" r:id="rId13"/>
+    <sheet name="CP-Z-2 EP" sheetId="15" r:id="rId14"/>
+    <sheet name="CP-Z-2 MF-I" sheetId="16" r:id="rId15"/>
+    <sheet name="CP-Z-2-B" sheetId="7" r:id="rId16"/>
+    <sheet name="Z-397 Guard" sheetId="10" r:id="rId17"/>
+    <sheet name="Z-397 Web" sheetId="11" r:id="rId18"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="116">
   <si>
     <t>8мА</t>
   </si>
@@ -592,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -634,107 +635,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -742,6 +647,117 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -779,7 +795,7 @@
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A129E10A-C5DD-46C6-DE20-84B1CE7FE078}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A129E10A-C5DD-46C6-DE20-84B1CE7FE078}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -828,7 +844,7 @@
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C18B9163-CE9A-45DD-882A-B22C6298A2B0}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C18B9163-CE9A-45DD-882A-B22C6298A2B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -877,7 +893,7 @@
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D8FB55A-B844-1D4B-88E1-A06600504B3E}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D8FB55A-B844-1D4B-88E1-A06600504B3E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1161,7 +1177,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1177,16 +1193,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1"/>
@@ -1209,10 +1225,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
@@ -1221,8 +1237,8 @@
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
@@ -1231,10 +1247,10 @@
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="38"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
@@ -1243,8 +1259,8 @@
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
@@ -1253,8 +1269,8 @@
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
@@ -1263,8 +1279,8 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
@@ -1273,8 +1289,8 @@
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
@@ -1283,10 +1299,10 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
@@ -1295,8 +1311,8 @@
       <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
@@ -1305,12 +1321,12 @@
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
@@ -1321,75 +1337,88 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="13">
         <v>1</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="31"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="13">
         <v>2</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="30"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="13">
         <v>3</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="13">
         <v>4</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
     </row>
     <row r="22" spans="1:4" ht="45" customHeight="1">
       <c r="A22" s="13">
         <v>5</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="13">
         <v>6</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A17:D17"/>
@@ -1397,19 +1426,6 @@
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -1417,6 +1433,241 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="36"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="E2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="2"/>
+      <c r="F3" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="37"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="34"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="54"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="54"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="34"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" customHeight="1">
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1">
+      <c r="A18" s="13">
+        <v>1</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
+    </row>
+    <row r="19" spans="1:4" ht="30" customHeight="1">
+      <c r="A19" s="13">
+        <v>2</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="30"/>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1">
+      <c r="A20" s="13">
+        <v>3</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1">
+      <c r="A21" s="13">
+        <v>4</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="13">
+        <v>5</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B18:D18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1426,16 +1677,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
@@ -1452,10 +1703,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
@@ -1464,10 +1715,10 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="19"/>
+      <c r="D5" s="34"/>
     </row>
     <row r="6" spans="1:6" ht="31.5" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -1476,8 +1727,8 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
@@ -1486,8 +1737,8 @@
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="1:6" ht="30.75" customHeight="1">
       <c r="A8" s="2" t="s">
@@ -1496,12 +1747,12 @@
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
@@ -1509,8 +1760,8 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
@@ -1521,27 +1772,33 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
     </row>
     <row r="17" spans="3:4">
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
@@ -1550,19 +1807,13 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1573,25 +1824,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="28"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="27"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="7" t="s">
@@ -1600,10 +1851,10 @@
       <c r="B4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="32"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="7" t="s">
         <v>42</v>
       </c>
@@ -1615,10 +1866,10 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="19"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="2" t="s">
         <v>45</v>
       </c>
@@ -1630,8 +1881,8 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="2" t="s">
         <v>46</v>
       </c>
@@ -1643,8 +1894,8 @@
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="2" t="s">
         <v>43</v>
       </c>
@@ -1656,8 +1907,8 @@
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="E8" s="2" t="s">
         <v>44</v>
       </c>
@@ -1669,8 +1920,8 @@
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="28"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="2" t="s">
         <v>50</v>
       </c>
@@ -1682,8 +1933,8 @@
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="28"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="27"/>
       <c r="E10" s="2" t="s">
         <v>51</v>
       </c>
@@ -1695,248 +1946,19 @@
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="28"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="2" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:D7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="14">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="14">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="21"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="19"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="28"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1">
-      <c r="A12" s="13">
-        <v>1</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="13">
-        <v>2</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="13">
-        <v>3</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="31"/>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1">
-      <c r="A15" s="13">
-        <v>4</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="31"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="13">
-        <v>5</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
@@ -1950,6 +1972,63 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="36"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="14">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="14">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F16"/>
@@ -1960,16 +2039,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
@@ -1986,10 +2065,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
@@ -1998,10 +2077,10 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="19"/>
+      <c r="D5" s="34"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
@@ -2010,28 +2089,28 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+        <v>18</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
@@ -2040,67 +2119,73 @@
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="28"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="27"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="13">
         <v>1</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="13">
         <v>2</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="13">
         <v>3</v>
       </c>
-      <c r="B14" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="31"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="B14" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="13">
         <v>4</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="31"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="13">
         <v>5</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="31"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="C8:D8"/>
@@ -2109,12 +2194,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2124,6 +2203,178 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="36"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="37"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="34"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="27"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="13">
+        <v>1</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="13">
+        <v>2</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="13">
+        <v>3</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="13">
+        <v>4</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="30"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="13">
+        <v>5</v>
+      </c>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2132,16 +2383,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
@@ -2158,10 +2409,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
@@ -2170,10 +2421,10 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="19"/>
+      <c r="D5" s="34"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
@@ -2182,36 +2433,36 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-    </row>
-    <row r="7" spans="1:6" s="56" customFormat="1" ht="94.5" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+    </row>
+    <row r="7" spans="1:6" s="24" customFormat="1" ht="94.5" customHeight="1">
+      <c r="A7" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="51" t="s">
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="52"/>
-    </row>
-    <row r="8" spans="1:6" s="56" customFormat="1" ht="101.25" customHeight="1">
-      <c r="A8" s="55" t="s">
+      <c r="F7" s="49"/>
+    </row>
+    <row r="8" spans="1:6" s="24" customFormat="1" ht="101.25" customHeight="1">
+      <c r="A8" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="51" t="s">
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="52"/>
+      <c r="F8" s="49"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
@@ -2261,9 +2512,9 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2283,7 +2534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2293,16 +2544,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
@@ -2319,10 +2570,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="7" t="s">
@@ -2331,10 +2582,10 @@
       <c r="B5" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="28"/>
+      <c r="D5" s="27"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="7" t="s">
@@ -2343,10 +2594,10 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="43"/>
+      <c r="D6" s="57"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="7" t="s">
@@ -2355,10 +2606,10 @@
       <c r="B7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="43"/>
+      <c r="D7" s="57"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="7" t="s">
@@ -2367,10 +2618,10 @@
       <c r="B8" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="43"/>
+      <c r="D8" s="57"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="7" t="s">
@@ -2379,10 +2630,10 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="43"/>
+      <c r="D9" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2400,7 +2651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2410,28 +2661,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="20" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
@@ -2448,10 +2699,10 @@
       <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="21"/>
+      <c r="D5" s="37"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="7" t="s">
@@ -2460,10 +2711,10 @@
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="28"/>
+      <c r="D6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="7" t="s">
@@ -2472,10 +2723,10 @@
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="31"/>
+      <c r="D7" s="30"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="7" t="s">
@@ -2484,8 +2735,8 @@
       <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="28"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="27"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="7" t="s">
@@ -2494,8 +2745,8 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="28"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="27"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="7" t="s">
@@ -2504,8 +2755,8 @@
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="28"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="7" t="s">
@@ -2514,8 +2765,8 @@
       <c r="B11" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="28"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="27"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="7" t="s">
@@ -2524,8 +2775,8 @@
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="28"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="27"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
@@ -2534,94 +2785,89 @@
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="28"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="27"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="15">
         <v>1</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="15">
         <v>2</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="15">
         <v>3</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="15">
         <v>4</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
     </row>
     <row r="20" spans="1:4" s="17" customFormat="1" ht="30" customHeight="1">
       <c r="A20" s="18">
         <v>5</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="15">
         <v>6</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="A22" s="15">
         <v>7</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C5:D5"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
@@ -2638,6 +2884,11 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2651,21 +2902,21 @@
   <cols>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
     <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="20" style="44" customWidth="1"/>
+    <col min="5" max="5" width="20" style="20" customWidth="1"/>
     <col min="6" max="6" width="9.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1"/>
@@ -2688,10 +2939,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6" ht="75">
       <c r="A5" s="2" t="s">
@@ -2700,9 +2951,9 @@
       <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="44" t="s">
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="20" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2713,9 +2964,9 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="44" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2726,8 +2977,8 @@
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
@@ -2736,8 +2987,8 @@
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
@@ -2746,8 +2997,8 @@
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
@@ -2756,8 +3007,8 @@
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
@@ -2766,10 +3017,10 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
@@ -2778,8 +3029,8 @@
       <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
@@ -2788,12 +3039,12 @@
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
@@ -2805,6 +3056,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
@@ -2812,12 +3069,6 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2834,16 +3085,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1"/>
@@ -2866,10 +3117,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
@@ -2878,8 +3129,8 @@
       <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
     </row>
     <row r="6" spans="1:6" ht="66.75" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -2888,12 +3139,12 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="51" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="52"/>
+      <c r="F6" s="49"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
@@ -2902,8 +3153,8 @@
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
@@ -2912,8 +3163,8 @@
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
@@ -2922,8 +3173,8 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="35"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="41"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
@@ -2932,8 +3183,8 @@
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
@@ -2942,10 +3193,10 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
@@ -2954,8 +3205,8 @@
       <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
@@ -2964,12 +3215,12 @@
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
@@ -2978,10 +3229,10 @@
       <c r="B15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="32"/>
+      <c r="D15" s="31"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
@@ -2990,8 +3241,8 @@
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
@@ -3000,8 +3251,8 @@
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
@@ -3010,37 +3261,41 @@
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="54"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="48.75" customHeight="1">
-      <c r="A21" s="33"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="54"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
@@ -3057,10 +3312,6 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B20:D21"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C7:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3077,16 +3328,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1"/>
@@ -3109,10 +3360,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="7" t="s">
@@ -3121,10 +3372,10 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="19"/>
+      <c r="D5" s="34"/>
     </row>
     <row r="6" spans="1:6" ht="29.25" customHeight="1">
       <c r="A6" s="7" t="s">
@@ -3133,10 +3384,10 @@
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="38"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="7" t="s">
@@ -3145,8 +3396,8 @@
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="1:6" ht="29.25" customHeight="1">
       <c r="A8" s="7" t="s">
@@ -3155,10 +3406,10 @@
       <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="24"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="7" t="s">
@@ -3167,8 +3418,8 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="7" t="s">
@@ -3177,8 +3428,8 @@
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="7" t="s">
@@ -3187,10 +3438,10 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="16" t="s">
@@ -3199,8 +3450,8 @@
       <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
@@ -3209,21 +3460,21 @@
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
@@ -3232,8 +3483,8 @@
       <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
@@ -3242,97 +3493,89 @@
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
     </row>
     <row r="19" spans="1:4" ht="59.25" customHeight="1">
       <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="A22" s="15">
         <v>1</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="15">
         <v>2</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="15">
         <v>3</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="31"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30"/>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1">
       <c r="A25" s="15">
         <v>4</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="30"/>
     </row>
     <row r="26" spans="1:4" ht="45" customHeight="1">
       <c r="A26" s="15">
         <v>5</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="31"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="15">
         <v>6</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
@@ -3349,6 +3592,14 @@
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3375,16 +3626,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1"/>
@@ -3413,10 +3664,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
@@ -3425,8 +3676,8 @@
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
@@ -3435,10 +3686,10 @@
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="38"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
@@ -3447,8 +3698,8 @@
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
@@ -3457,8 +3708,8 @@
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
@@ -3467,8 +3718,8 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
@@ -3477,8 +3728,8 @@
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
@@ -3487,10 +3738,10 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
@@ -3499,8 +3750,8 @@
       <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
@@ -3509,108 +3760,99 @@
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="8">
         <v>1</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="31"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="30"/>
     </row>
     <row r="18" spans="1:4" s="9" customFormat="1" ht="30.75" customHeight="1">
       <c r="A18" s="10">
         <v>2</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="31"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
     </row>
     <row r="19" spans="1:4" s="12" customFormat="1">
       <c r="A19" s="11">
         <v>3</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="52"/>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="8">
         <v>4</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
     </row>
     <row r="21" spans="1:4" ht="45" customHeight="1">
       <c r="A21" s="8">
         <v>5</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="A22" s="8">
         <v>6</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="8">
         <v>7</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="8">
         <v>8</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="28"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
@@ -3623,6 +3865,15 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3641,6 +3892,275 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="60.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="36"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="37"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="38"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="38"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="34"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+    </row>
+    <row r="17" spans="1:6" s="20" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A17" s="58">
+        <v>1</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="29"/>
+      <c r="D17" s="30"/>
+    </row>
+    <row r="18" spans="1:6" s="20" customFormat="1">
+      <c r="A18" s="10">
+        <v>2</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" s="20" customFormat="1">
+      <c r="A19" s="10">
+        <v>3</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" s="20" customFormat="1">
+      <c r="A20" s="58">
+        <v>4</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
+    </row>
+    <row r="21" spans="1:6" s="20" customFormat="1">
+      <c r="A21" s="58">
+        <v>5</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+    </row>
+    <row r="22" spans="1:6" s="20" customFormat="1" ht="30" customHeight="1">
+      <c r="A22" s="58">
+        <v>6</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
+    </row>
+    <row r="23" spans="1:6" s="20" customFormat="1">
+      <c r="A23" s="58">
+        <v>7</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+    </row>
+    <row r="24" spans="1:6" s="20" customFormat="1">
+      <c r="A24" s="58">
+        <v>8</v>
+      </c>
+      <c r="B24" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="60"/>
+      <c r="D24" s="61"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3649,16 +4169,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1"/>
@@ -3687,10 +4207,10 @@
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
@@ -3699,8 +4219,8 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
@@ -3709,8 +4229,8 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
@@ -3719,8 +4239,8 @@
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
@@ -3729,8 +4249,8 @@
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:6" ht="30.75" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -3739,10 +4259,10 @@
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="40"/>
+      <c r="D9" s="54"/>
     </row>
     <row r="10" spans="1:6" ht="30.75" customHeight="1">
       <c r="A10" s="2" t="s">
@@ -3751,10 +4271,10 @@
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="40"/>
+      <c r="D10" s="54"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
@@ -3763,93 +4283,98 @@
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="19"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="13">
         <v>1</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="31"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="13">
         <v>2</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="30"/>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="13">
         <v>3</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="13">
         <v>4</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="13">
         <v>5</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="C7:D7"/>
@@ -3864,246 +4389,6 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="E2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2"/>
-      <c r="F3" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="21"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="19"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="40"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="40"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="19"/>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1">
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-    </row>
-    <row r="18" spans="1:4" ht="30" customHeight="1">
-      <c r="A18" s="13">
-        <v>1</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="31"/>
-    </row>
-    <row r="19" spans="1:4" ht="30" customHeight="1">
-      <c r="A19" s="13">
-        <v>2</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
-    </row>
-    <row r="20" spans="1:4" ht="30" customHeight="1">
-      <c r="A20" s="13">
-        <v>3</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
-    </row>
-    <row r="21" spans="1:4" ht="30" customHeight="1">
-      <c r="A21" s="13">
-        <v>4</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="13">
-        <v>5</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
